--- a/outputs/39667.xlsx
+++ b/outputs/39667.xlsx
@@ -228,52 +228,56 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -604,400 +608,400 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="true" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="56.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="31.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="36.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="56.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="20.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="36.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C3,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C4,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C5,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C6,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C7,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C8,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C9,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C10,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C11,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C12,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C13,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C14,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C15,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C16,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="5" t="n">
         <f aca="false">SUMIF(Table2[Description],C17,Table2[Quantity Installed])</f>
         <v>0</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" s="6" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" s="7" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
-        <f aca="false">IF(C20="","",INDEX(Table3[Pay Item Number],MATCH(C20,Table3[Description],0)))</f>
+      <c r="A20" s="11" t="n">
+        <f aca="false">IF(C20="","",INDEX($A$3:$A$17,MATCH(C20,$C$3:$C$17,0)))</f>
         <v>12</v>
       </c>
-      <c r="B20" s="10" t="str">
-        <f aca="false">IF(C20="","",INDEX(Table3[UOM],MATCH(C20,Table3[Description],0)))</f>
+      <c r="B20" s="11" t="str">
+        <f aca="false">IF(C20="","",INDEX($B$3:$B$17,MATCH(C20,$C$3:$C$17,0)))</f>
         <v>LF</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="n">
-        <f aca="false">IF(C21="","",INDEX(Table3[Pay Item Number],MATCH(C21,Table3[Description],0)))</f>
+      <c r="A21" s="11" t="n">
+        <f aca="false">IF(C21="","",INDEX($A$3:$A$17,MATCH(C21,$C$3:$C$17,0)))</f>
         <v>10</v>
       </c>
-      <c r="B21" s="10" t="str">
-        <f aca="false">IF(C21="","",INDEX(Table3[UOM],MATCH(C21,Table3[Description],0)))</f>
+      <c r="B21" s="11" t="str">
+        <f aca="false">IF(C21="","",INDEX($B$3:$B$17,MATCH(C21,$C$3:$C$17,0)))</f>
         <v>LB</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="str">
-        <f aca="false">IF(C22="","",INDEX(Table3[Pay Item Number],MATCH(C22,Table3[Description],0)))</f>
+      <c r="A22" s="11" t="str">
+        <f aca="false">IF(C22="","",INDEX($A$3:$A$17,MATCH(C22,$C$3:$C$17,0)))</f>
         <v/>
       </c>
-      <c r="B22" s="10" t="str">
-        <f aca="false">IF(C22="","",INDEX(Table3[UOM],MATCH(C22,Table3[Description],0)))</f>
+      <c r="B22" s="11" t="str">
+        <f aca="false">IF(C22="","",INDEX($B$3:$B$17,MATCH(C22,$C$3:$C$17,0)))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="str">
-        <f aca="false">IF(C23="","",INDEX(Table3[Pay Item Number],MATCH(C23,Table3[Description],0)))</f>
+      <c r="A23" s="11" t="str">
+        <f aca="false">IF(C23="","",INDEX($A$3:$A$17,MATCH(C23,$C$3:$C$17,0)))</f>
         <v/>
       </c>
-      <c r="B23" s="10" t="str">
-        <f aca="false">IF(C23="","",INDEX(Table3[UOM],MATCH(C23,Table3[Description],0)))</f>
+      <c r="B23" s="11" t="str">
+        <f aca="false">IF(C23="","",INDEX($B$3:$B$17,MATCH(C23,$C$3:$C$17,0)))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="str">
-        <f aca="false">IF(C24="","",INDEX(Table3[Pay Item Number],MATCH(C24,Table3[Description],0)))</f>
+      <c r="A24" s="11" t="str">
+        <f aca="false">IF(C24="","",INDEX($A$3:$A$17,MATCH(C24,$C$3:$C$17,0)))</f>
         <v/>
       </c>
-      <c r="B24" s="10" t="str">
-        <f aca="false">IF(C24="","",INDEX(Table3[UOM],MATCH(C24,Table3[Description],0)))</f>
+      <c r="B24" s="11" t="str">
+        <f aca="false">IF(C24="","",INDEX($B$3:$B$17,MATCH(C24,$C$3:$C$17,0)))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="str">
-        <f aca="false">IF(C25="","",INDEX(Table3[Pay Item Number],MATCH(C25,Table3[Description],0)))</f>
+      <c r="A25" s="11" t="str">
+        <f aca="false">IF(C25="","",INDEX($A$3:$A$17,MATCH(C25,$C$3:$C$17,0)))</f>
         <v/>
       </c>
-      <c r="B25" s="10" t="str">
-        <f aca="false">IF(C25="","",INDEX(Table3[UOM],MATCH(C25,Table3[Description],0)))</f>
+      <c r="B25" s="11" t="str">
+        <f aca="false">IF(C25="","",INDEX($B$3:$B$17,MATCH(C25,$C$3:$C$17,0)))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="str">
-        <f aca="false">IF(C26="","",INDEX(Table3[Pay Item Number],MATCH(C26,Table3[Description],0)))</f>
+      <c r="A26" s="11" t="str">
+        <f aca="false">IF(C26="","",INDEX($A$3:$A$17,MATCH(C26,$C$3:$C$17,0)))</f>
         <v/>
       </c>
-      <c r="B26" s="10" t="str">
-        <f aca="false">IF(C26="","",INDEX(Table3[UOM],MATCH(C26,Table3[Description],0)))</f>
+      <c r="B26" s="11" t="str">
+        <f aca="false">IF(C26="","",INDEX($B$3:$B$17,MATCH(C26,$C$3:$C$17,0)))</f>
         <v/>
       </c>
     </row>
